--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.9.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.9.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.9.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.9.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="39" customWidth="1" min="14" max="14"/>
     <col width="39" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.9.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.9.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0009.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0009.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -598,11 +598,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢tion with, or effect upon, the provisions of the former Orders.X</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]INTRODUCTORY REMARKS.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]INTRODUCTORY REMARKS.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L15: isolated marker/symbol line :: S</t>
@@ -616,7 +620,11 @@
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L10: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •tion with, or effect upon, the provisions of the former Orders.X</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -637,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: institutionâ€”that, like many other creatures of Canadian Parliamentary</t>
+          <t>L10: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •tion with, or effect upon, the provisions of the former Orders.X</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -957,7 +965,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1074,7 +1082,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
